--- a/data.xlsx
+++ b/data.xlsx
@@ -957,7 +957,7 @@
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
       <c r="J10" s="2">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
@@ -991,7 +991,7 @@
       </c>
       <c r="AK10" s="2">
         <f t="shared" si="0"/>
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AL10" s="2"/>
     </row>
@@ -1570,7 +1570,7 @@
       <c r="AK23" s="2"/>
       <c r="AL23" s="2">
         <f>SUM(AK4:AK15)</f>
-        <v>3103</v>
+        <v>3303</v>
       </c>
     </row>
     <row r="24" spans="1:38" x14ac:dyDescent="0.25">

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>ҳисоботи як моҳаи маблағи захиравии деҳаи марғеб</t>
   </si>
@@ -67,6 +67,24 @@
   </si>
   <si>
     <t>Баҳромов Акобир</t>
+  </si>
+  <si>
+    <t>Муллоев Раҳматулло</t>
+  </si>
+  <si>
+    <t>Саломов Саидалӣ</t>
+  </si>
+  <si>
+    <t>Пиров Мирзоумед</t>
+  </si>
+  <si>
+    <t>Ҳасанов Мирзораҳмат</t>
+  </si>
+  <si>
+    <t>Маликов Айёмиддин</t>
+  </si>
+  <si>
+    <t>Латифов Қурбон</t>
   </si>
 </sst>
 </file>
@@ -420,11 +438,13 @@
     <col min="2" max="2" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.7109375" style="1" customWidth="1"/>
     <col min="4" max="9" width="2" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="2" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="34" width="3" style="1" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="21.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="21.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -727,7 +747,7 @@
         <v>927774967</v>
       </c>
       <c r="AK5" s="2">
-        <f t="shared" ref="AK5:AK15" si="0">D5+E5+F5+G5+H5+I5+J5+K5+L5+M5+N5+O5+P5+Q5+R5+S5+T5+U5+V5+W5+X5+Y5+Z5+AA5+AB5+AC5+AD5+AE5+AF5+AG5+AH5</f>
+        <f t="shared" ref="AK5:AK23" si="0">D5+E5+F5+G5+H5+I5+J5+K5+L5+M5+N5+O5+P5+Q5+R5+S5+T5+U5+V5+W5+X5+Y5+Z5+AA5+AB5+AC5+AD5+AE5+AF5+AG5+AH5</f>
         <v>300</v>
       </c>
       <c r="AL5" s="2"/>
@@ -1052,7 +1072,9 @@
       <c r="A12" s="2">
         <v>9</v>
       </c>
-      <c r="B12" s="2"/>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
@@ -1061,7 +1083,9 @@
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+      <c r="K12" s="2">
+        <v>300</v>
+      </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
@@ -1085,13 +1109,15 @@
       <c r="AF12" s="2"/>
       <c r="AG12" s="2"/>
       <c r="AH12" s="2"/>
-      <c r="AI12" s="2"/>
+      <c r="AI12" s="2">
+        <v>1605921943</v>
+      </c>
       <c r="AJ12" s="2">
         <v>927774967</v>
       </c>
       <c r="AK12" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AL12" s="2"/>
     </row>
@@ -1099,7 +1125,9 @@
       <c r="A13" s="2">
         <v>10</v>
       </c>
-      <c r="B13" s="2"/>
+      <c r="B13" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
@@ -1108,7 +1136,9 @@
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="K13" s="2">
+        <v>300</v>
+      </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -1132,13 +1162,15 @@
       <c r="AF13" s="2"/>
       <c r="AG13" s="2"/>
       <c r="AH13" s="2"/>
-      <c r="AI13" s="2"/>
+      <c r="AI13" s="2">
+        <v>146768691</v>
+      </c>
       <c r="AJ13" s="2">
         <v>927774967</v>
       </c>
       <c r="AK13" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AL13" s="2"/>
     </row>
@@ -1146,7 +1178,9 @@
       <c r="A14" s="2">
         <v>11</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
@@ -1155,7 +1189,9 @@
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
+      <c r="K14" s="2">
+        <v>300</v>
+      </c>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -1179,13 +1215,15 @@
       <c r="AF14" s="2"/>
       <c r="AG14" s="2"/>
       <c r="AH14" s="2"/>
-      <c r="AI14" s="2"/>
+      <c r="AI14" s="2">
+        <v>78859110</v>
+      </c>
       <c r="AJ14" s="2">
         <v>927774967</v>
       </c>
       <c r="AK14" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AL14" s="2"/>
     </row>
@@ -1193,7 +1231,9 @@
       <c r="A15" s="2">
         <v>12</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" s="2" t="s">
+        <v>19</v>
+      </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
@@ -1202,7 +1242,9 @@
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
+      <c r="K15" s="2">
+        <v>300</v>
+      </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
@@ -1227,10 +1269,12 @@
       <c r="AG15" s="2"/>
       <c r="AH15" s="2"/>
       <c r="AI15" s="2"/>
-      <c r="AJ15" s="2"/>
+      <c r="AJ15" s="2">
+        <v>927774967</v>
+      </c>
       <c r="AK15" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AL15" s="2"/>
     </row>
@@ -1238,7 +1282,9 @@
       <c r="A16" s="2">
         <v>13</v>
       </c>
-      <c r="B16" s="2"/>
+      <c r="B16" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
@@ -1247,7 +1293,9 @@
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
+      <c r="K16" s="2">
+        <v>300</v>
+      </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
@@ -1271,16 +1319,25 @@
       <c r="AF16" s="2"/>
       <c r="AG16" s="2"/>
       <c r="AH16" s="2"/>
-      <c r="AI16" s="2"/>
-      <c r="AJ16" s="2"/>
-      <c r="AK16" s="2"/>
+      <c r="AI16" s="2">
+        <v>146638491</v>
+      </c>
+      <c r="AJ16" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK16" s="2">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
       <c r="AL16" s="2"/>
     </row>
     <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>14</v>
       </c>
-      <c r="B17" s="2"/>
+      <c r="B17" s="2" t="s">
+        <v>21</v>
+      </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
@@ -1289,7 +1346,9 @@
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
+      <c r="K17" s="2">
+        <v>300</v>
+      </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
@@ -1313,9 +1372,16 @@
       <c r="AF17" s="2"/>
       <c r="AG17" s="2"/>
       <c r="AH17" s="2"/>
-      <c r="AI17" s="2"/>
-      <c r="AJ17" s="2"/>
-      <c r="AK17" s="2"/>
+      <c r="AI17" s="2">
+        <v>146636404</v>
+      </c>
+      <c r="AJ17" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK17" s="2">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
       <c r="AL17" s="2"/>
     </row>
     <row r="18" spans="1:38" x14ac:dyDescent="0.25">
@@ -1356,8 +1422,13 @@
       <c r="AG18" s="2"/>
       <c r="AH18" s="2"/>
       <c r="AI18" s="2"/>
-      <c r="AJ18" s="2"/>
-      <c r="AK18" s="2"/>
+      <c r="AJ18" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK18" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="AL18" s="2"/>
     </row>
     <row r="19" spans="1:38" x14ac:dyDescent="0.25">
@@ -1398,8 +1469,13 @@
       <c r="AG19" s="2"/>
       <c r="AH19" s="2"/>
       <c r="AI19" s="2"/>
-      <c r="AJ19" s="2"/>
-      <c r="AK19" s="2"/>
+      <c r="AJ19" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK19" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="AL19" s="2"/>
     </row>
     <row r="20" spans="1:38" x14ac:dyDescent="0.25">
@@ -1440,8 +1516,13 @@
       <c r="AG20" s="2"/>
       <c r="AH20" s="2"/>
       <c r="AI20" s="2"/>
-      <c r="AJ20" s="2"/>
-      <c r="AK20" s="2"/>
+      <c r="AJ20" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK20" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="AL20" s="2"/>
     </row>
     <row r="21" spans="1:38" x14ac:dyDescent="0.25">
@@ -1482,8 +1563,13 @@
       <c r="AG21" s="2"/>
       <c r="AH21" s="2"/>
       <c r="AI21" s="2"/>
-      <c r="AJ21" s="2"/>
-      <c r="AK21" s="2"/>
+      <c r="AJ21" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK21" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="AL21" s="2"/>
     </row>
     <row r="22" spans="1:38" x14ac:dyDescent="0.25">
@@ -1524,8 +1610,13 @@
       <c r="AG22" s="2"/>
       <c r="AH22" s="2"/>
       <c r="AI22" s="2"/>
-      <c r="AJ22" s="2"/>
-      <c r="AK22" s="2"/>
+      <c r="AJ22" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK22" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="AL22" s="2"/>
     </row>
     <row r="23" spans="1:38" x14ac:dyDescent="0.25">
@@ -1566,134 +1657,509 @@
       <c r="AG23" s="2"/>
       <c r="AH23" s="2"/>
       <c r="AI23" s="2"/>
-      <c r="AJ23" s="2"/>
-      <c r="AK23" s="2"/>
+      <c r="AJ23" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK23" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="AL23" s="2">
-        <f>SUM(AK4:AK15)</f>
-        <v>3303</v>
+        <f>SUM(AK4:AK23)</f>
+        <v>5103</v>
       </c>
     </row>
     <row r="24" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A24" s="1">
+      <c r="A24" s="2">
         <v>21</v>
       </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="2"/>
+      <c r="Z24" s="2"/>
+      <c r="AA24" s="2"/>
+      <c r="AB24" s="2"/>
+      <c r="AC24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AE24" s="2"/>
+      <c r="AF24" s="2"/>
+      <c r="AG24" s="2"/>
+      <c r="AH24" s="2"/>
+      <c r="AI24" s="2"/>
+      <c r="AJ24" s="2"/>
+      <c r="AK24" s="2"/>
+      <c r="AL24" s="2"/>
     </row>
     <row r="25" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A25" s="1">
+      <c r="A25" s="2">
         <v>22</v>
       </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="2"/>
+      <c r="Z25" s="2"/>
+      <c r="AA25" s="2"/>
+      <c r="AB25" s="2"/>
+      <c r="AC25" s="2"/>
+      <c r="AD25" s="2"/>
+      <c r="AE25" s="2"/>
+      <c r="AF25" s="2"/>
+      <c r="AG25" s="2"/>
+      <c r="AH25" s="2"/>
+      <c r="AI25" s="2"/>
+      <c r="AJ25" s="2"/>
+      <c r="AK25" s="2"/>
+      <c r="AL25" s="2"/>
     </row>
     <row r="26" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A26" s="1">
+      <c r="A26" s="2">
         <v>23</v>
       </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="2"/>
+      <c r="Z26" s="2"/>
+      <c r="AA26" s="2"/>
+      <c r="AB26" s="2"/>
+      <c r="AC26" s="2"/>
+      <c r="AD26" s="2"/>
+      <c r="AE26" s="2"/>
+      <c r="AF26" s="2"/>
+      <c r="AG26" s="2"/>
+      <c r="AH26" s="2"/>
+      <c r="AI26" s="2"/>
+      <c r="AJ26" s="2"/>
+      <c r="AK26" s="2"/>
+      <c r="AL26" s="2"/>
     </row>
     <row r="27" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A27" s="1">
+      <c r="A27" s="2">
         <v>24</v>
       </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="2"/>
+      <c r="Z27" s="2"/>
+      <c r="AA27" s="2"/>
+      <c r="AB27" s="2"/>
+      <c r="AC27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AE27" s="2"/>
+      <c r="AF27" s="2"/>
+      <c r="AG27" s="2"/>
+      <c r="AH27" s="2"/>
+      <c r="AI27" s="2"/>
+      <c r="AJ27" s="2"/>
+      <c r="AK27" s="2"/>
+      <c r="AL27" s="2"/>
     </row>
     <row r="28" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A28" s="1">
+      <c r="A28" s="2">
         <v>25</v>
       </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="2"/>
+      <c r="Z28" s="2"/>
+      <c r="AA28" s="2"/>
+      <c r="AB28" s="2"/>
+      <c r="AC28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AE28" s="2"/>
+      <c r="AF28" s="2"/>
+      <c r="AG28" s="2"/>
+      <c r="AH28" s="2"/>
+      <c r="AI28" s="2"/>
+      <c r="AJ28" s="2"/>
+      <c r="AK28" s="2"/>
+      <c r="AL28" s="2"/>
     </row>
     <row r="29" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A29" s="1">
+      <c r="A29" s="2">
         <v>26</v>
       </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+      <c r="Y29" s="2"/>
+      <c r="Z29" s="2"/>
+      <c r="AA29" s="2"/>
+      <c r="AB29" s="2"/>
+      <c r="AC29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AE29" s="2"/>
+      <c r="AF29" s="2"/>
+      <c r="AG29" s="2"/>
+      <c r="AH29" s="2"/>
+      <c r="AI29" s="2"/>
+      <c r="AJ29" s="2"/>
+      <c r="AK29" s="2"/>
+      <c r="AL29" s="2"/>
     </row>
     <row r="30" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A30" s="1">
+      <c r="A30" s="2">
         <v>27</v>
       </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="2"/>
+      <c r="Z30" s="2"/>
+      <c r="AA30" s="2"/>
+      <c r="AB30" s="2"/>
+      <c r="AC30" s="2"/>
+      <c r="AD30" s="2"/>
+      <c r="AE30" s="2"/>
+      <c r="AF30" s="2"/>
+      <c r="AG30" s="2"/>
+      <c r="AH30" s="2"/>
+      <c r="AI30" s="2"/>
+      <c r="AJ30" s="2"/>
+      <c r="AK30" s="2"/>
+      <c r="AL30" s="2"/>
     </row>
     <row r="31" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A31" s="1">
+      <c r="A31" s="2">
         <v>28</v>
       </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="2"/>
+      <c r="Z31" s="2"/>
+      <c r="AA31" s="2"/>
+      <c r="AB31" s="2"/>
+      <c r="AC31" s="2"/>
+      <c r="AD31" s="2"/>
+      <c r="AE31" s="2"/>
+      <c r="AF31" s="2"/>
+      <c r="AG31" s="2"/>
+      <c r="AH31" s="2"/>
+      <c r="AI31" s="2"/>
+      <c r="AJ31" s="2"/>
+      <c r="AK31" s="2"/>
+      <c r="AL31" s="2"/>
     </row>
     <row r="32" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A32" s="1">
+      <c r="A32" s="2">
         <v>29</v>
       </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="1">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+      <c r="Y32" s="2"/>
+      <c r="Z32" s="2"/>
+      <c r="AA32" s="2"/>
+      <c r="AB32" s="2"/>
+      <c r="AC32" s="2"/>
+      <c r="AD32" s="2"/>
+      <c r="AE32" s="2"/>
+      <c r="AF32" s="2"/>
+      <c r="AG32" s="2"/>
+      <c r="AH32" s="2"/>
+      <c r="AI32" s="2"/>
+      <c r="AJ32" s="2"/>
+      <c r="AK32" s="2"/>
+      <c r="AL32" s="2"/>
+    </row>
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
         <v>30</v>
       </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
+      <c r="X33" s="2"/>
+      <c r="Y33" s="2"/>
+      <c r="Z33" s="2"/>
+      <c r="AA33" s="2"/>
+      <c r="AB33" s="2"/>
+      <c r="AC33" s="2"/>
+      <c r="AD33" s="2"/>
+      <c r="AE33" s="2"/>
+      <c r="AF33" s="2"/>
+      <c r="AG33" s="2"/>
+      <c r="AH33" s="2"/>
+      <c r="AI33" s="2"/>
+      <c r="AJ33" s="2"/>
+      <c r="AK33" s="2"/>
+      <c r="AL33" s="2"/>
+    </row>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>37</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>38</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>41</v>
       </c>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>43</v>
       </c>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>44</v>
       </c>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>45</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1776,10 +1776,9 @@
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
-      <c r="I24" s="2">
-        <v>300</v>
-      </c>
-      <c r="J24" s="2"/>
+      <c r="J24" s="2">
+        <v>300</v>
+      </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -1882,10 +1881,9 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
-      <c r="I26" s="2">
-        <v>300</v>
-      </c>
-      <c r="J26" s="2"/>
+      <c r="J26" s="2">
+        <v>300</v>
+      </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -1935,10 +1933,9 @@
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-      <c r="I27" s="2">
-        <v>300</v>
-      </c>
-      <c r="J27" s="2"/>
+      <c r="J27" s="2">
+        <v>300</v>
+      </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -2147,10 +2144,9 @@
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
-      <c r="I31" s="2">
-        <v>300</v>
-      </c>
-      <c r="J31" s="2"/>
+      <c r="J31" s="2">
+        <v>300</v>
+      </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
   <si>
     <t xml:space="preserve">ном ва насаб </t>
   </si>
@@ -130,6 +130,21 @@
   </si>
   <si>
     <t>Дустов Рустамбек</t>
+  </si>
+  <si>
+    <t>Аслиддинов Баҳриддин</t>
+  </si>
+  <si>
+    <t>Шоев Мирзоумар</t>
+  </si>
+  <si>
+    <t>Гулов Муҳаммадризо</t>
+  </si>
+  <si>
+    <t>Гулов Субҳон</t>
+  </si>
+  <si>
+    <t>Гулов Қурбон</t>
   </si>
 </sst>
 </file>
@@ -503,7 +518,9 @@
     <col min="11" max="11" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="34" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="4.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="34" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -810,7 +827,7 @@
         <v>927774967</v>
       </c>
       <c r="AK5" s="2">
-        <f t="shared" ref="AK5:AK33" si="0">SUM(D5:AH5)</f>
+        <f t="shared" ref="AK5:AK43" si="0">SUM(D5:AH5)</f>
         <v>300</v>
       </c>
       <c r="AL5" s="2"/>
@@ -2187,7 +2204,9 @@
       <c r="A32" s="2">
         <v>29</v>
       </c>
-      <c r="B32" s="2"/>
+      <c r="B32" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
@@ -2202,7 +2221,9 @@
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" s="2"/>
-      <c r="Q32" s="2"/>
+      <c r="Q32" s="2">
+        <v>300</v>
+      </c>
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
       <c r="T32" s="2"/>
@@ -2220,13 +2241,15 @@
       <c r="AF32" s="2"/>
       <c r="AG32" s="2"/>
       <c r="AH32" s="2"/>
-      <c r="AI32" s="3"/>
+      <c r="AI32" s="3">
+        <v>148505505</v>
+      </c>
       <c r="AJ32" s="2">
         <v>927774967</v>
       </c>
       <c r="AK32" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="AL32" s="2"/>
     </row>
@@ -2234,7 +2257,9 @@
       <c r="A33" s="2">
         <v>30</v>
       </c>
-      <c r="B33" s="2"/>
+      <c r="B33" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
@@ -2248,7 +2273,9 @@
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
-      <c r="P33" s="2"/>
+      <c r="P33" s="2">
+        <v>300</v>
+      </c>
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
@@ -2273,432 +2300,494 @@
       </c>
       <c r="AK33" s="2">
         <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="AL33" s="2"/>
+    </row>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A34" s="2">
+        <v>31</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2">
+        <v>300</v>
+      </c>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+      <c r="Y34" s="2"/>
+      <c r="Z34" s="2"/>
+      <c r="AA34" s="2"/>
+      <c r="AB34" s="2"/>
+      <c r="AC34" s="2"/>
+      <c r="AD34" s="2"/>
+      <c r="AE34" s="2"/>
+      <c r="AF34" s="2"/>
+      <c r="AG34" s="2"/>
+      <c r="AH34" s="2"/>
+      <c r="AI34" s="2"/>
+      <c r="AJ34" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK34" s="2">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="AL34" s="2"/>
+    </row>
+    <row r="35" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A35" s="2">
+        <v>32</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2">
+        <v>303</v>
+      </c>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="2"/>
+      <c r="X35" s="2"/>
+      <c r="Y35" s="2"/>
+      <c r="Z35" s="2"/>
+      <c r="AA35" s="2"/>
+      <c r="AB35" s="2"/>
+      <c r="AC35" s="2"/>
+      <c r="AD35" s="2"/>
+      <c r="AE35" s="2"/>
+      <c r="AF35" s="2"/>
+      <c r="AG35" s="2"/>
+      <c r="AH35" s="2"/>
+      <c r="AI35" s="2"/>
+      <c r="AJ35" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK35" s="2">
+        <f t="shared" si="0"/>
+        <v>303</v>
+      </c>
+      <c r="AL35" s="2"/>
+    </row>
+    <row r="36" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A36" s="2">
+        <v>33</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2">
+        <v>304</v>
+      </c>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="2"/>
+      <c r="X36" s="2"/>
+      <c r="Y36" s="2"/>
+      <c r="Z36" s="2"/>
+      <c r="AA36" s="2"/>
+      <c r="AB36" s="2"/>
+      <c r="AC36" s="2"/>
+      <c r="AD36" s="2"/>
+      <c r="AE36" s="2"/>
+      <c r="AF36" s="2"/>
+      <c r="AG36" s="2"/>
+      <c r="AH36" s="2"/>
+      <c r="AI36" s="2"/>
+      <c r="AJ36" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK36" s="2">
+        <f t="shared" si="0"/>
+        <v>304</v>
+      </c>
+      <c r="AL36" s="2"/>
+    </row>
+    <row r="37" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A37" s="2">
+        <v>34</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
+      <c r="W37" s="2"/>
+      <c r="X37" s="2"/>
+      <c r="Y37" s="2"/>
+      <c r="Z37" s="2"/>
+      <c r="AA37" s="2"/>
+      <c r="AB37" s="2"/>
+      <c r="AC37" s="2"/>
+      <c r="AD37" s="2"/>
+      <c r="AE37" s="2"/>
+      <c r="AF37" s="2"/>
+      <c r="AG37" s="2"/>
+      <c r="AH37" s="2"/>
+      <c r="AI37" s="2"/>
+      <c r="AJ37" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK37" s="2">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AL33" s="2">
-        <f>SUM(AK4:AK33)</f>
-        <v>10009</v>
-      </c>
-    </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A34" s="4">
-        <v>31</v>
-      </c>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4"/>
-      <c r="T34" s="4"/>
-      <c r="U34" s="4"/>
-      <c r="V34" s="4"/>
-      <c r="W34" s="4"/>
-      <c r="X34" s="4"/>
-      <c r="Y34" s="4"/>
-      <c r="Z34" s="4"/>
-      <c r="AA34" s="4"/>
-      <c r="AB34" s="4"/>
-      <c r="AC34" s="4"/>
-      <c r="AD34" s="4"/>
-      <c r="AE34" s="4"/>
-      <c r="AF34" s="4"/>
-      <c r="AG34" s="4"/>
-      <c r="AH34" s="4"/>
-      <c r="AI34" s="4"/>
-      <c r="AJ34" s="4"/>
-      <c r="AK34" s="4"/>
-      <c r="AL34" s="4"/>
-    </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A35" s="4">
-        <v>32</v>
-      </c>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="4"/>
-      <c r="W35" s="4"/>
-      <c r="X35" s="4"/>
-      <c r="Y35" s="4"/>
-      <c r="Z35" s="4"/>
-      <c r="AA35" s="4"/>
-      <c r="AB35" s="4"/>
-      <c r="AC35" s="4"/>
-      <c r="AD35" s="4"/>
-      <c r="AE35" s="4"/>
-      <c r="AF35" s="4"/>
-      <c r="AG35" s="4"/>
-      <c r="AH35" s="4"/>
-      <c r="AI35" s="4"/>
-      <c r="AJ35" s="4"/>
-      <c r="AK35" s="4"/>
-      <c r="AL35" s="4"/>
-    </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A36" s="4">
-        <v>33</v>
-      </c>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="4"/>
-      <c r="W36" s="4"/>
-      <c r="X36" s="4"/>
-      <c r="Y36" s="4"/>
-      <c r="Z36" s="4"/>
-      <c r="AA36" s="4"/>
-      <c r="AB36" s="4"/>
-      <c r="AC36" s="4"/>
-      <c r="AD36" s="4"/>
-      <c r="AE36" s="4"/>
-      <c r="AF36" s="4"/>
-      <c r="AG36" s="4"/>
-      <c r="AH36" s="4"/>
-      <c r="AI36" s="4"/>
-      <c r="AJ36" s="4"/>
-      <c r="AK36" s="4"/>
-      <c r="AL36" s="4"/>
-    </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A37" s="4">
-        <v>34</v>
-      </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
-      <c r="R37" s="4"/>
-      <c r="S37" s="4"/>
-      <c r="T37" s="4"/>
-      <c r="U37" s="4"/>
-      <c r="V37" s="4"/>
-      <c r="W37" s="4"/>
-      <c r="X37" s="4"/>
-      <c r="Y37" s="4"/>
-      <c r="Z37" s="4"/>
-      <c r="AA37" s="4"/>
-      <c r="AB37" s="4"/>
-      <c r="AC37" s="4"/>
-      <c r="AD37" s="4"/>
-      <c r="AE37" s="4"/>
-      <c r="AF37" s="4"/>
-      <c r="AG37" s="4"/>
-      <c r="AH37" s="4"/>
-      <c r="AI37" s="4"/>
-      <c r="AJ37" s="4"/>
-      <c r="AK37" s="4"/>
-      <c r="AL37" s="4"/>
+      <c r="AL37" s="2"/>
     </row>
     <row r="38" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A38" s="4">
+      <c r="A38" s="2">
         <v>35</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="4"/>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
-      <c r="R38" s="4"/>
-      <c r="S38" s="4"/>
-      <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
-      <c r="V38" s="4"/>
-      <c r="W38" s="4"/>
-      <c r="X38" s="4"/>
-      <c r="Y38" s="4"/>
-      <c r="Z38" s="4"/>
-      <c r="AA38" s="4"/>
-      <c r="AB38" s="4"/>
-      <c r="AC38" s="4"/>
-      <c r="AD38" s="4"/>
-      <c r="AE38" s="4"/>
-      <c r="AF38" s="4"/>
-      <c r="AG38" s="4"/>
-      <c r="AH38" s="4"/>
-      <c r="AI38" s="4"/>
-      <c r="AJ38" s="4"/>
-      <c r="AK38" s="4"/>
-      <c r="AL38" s="4"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2"/>
+      <c r="W38" s="2"/>
+      <c r="X38" s="2"/>
+      <c r="Y38" s="2"/>
+      <c r="Z38" s="2"/>
+      <c r="AA38" s="2"/>
+      <c r="AB38" s="2"/>
+      <c r="AC38" s="2"/>
+      <c r="AD38" s="2"/>
+      <c r="AE38" s="2"/>
+      <c r="AF38" s="2"/>
+      <c r="AG38" s="2"/>
+      <c r="AH38" s="2"/>
+      <c r="AI38" s="2"/>
+      <c r="AJ38" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK38" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL38" s="2"/>
     </row>
     <row r="39" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A39" s="4">
+      <c r="A39" s="2">
         <v>36</v>
       </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-      <c r="Q39" s="4"/>
-      <c r="R39" s="4"/>
-      <c r="S39" s="4"/>
-      <c r="T39" s="4"/>
-      <c r="U39" s="4"/>
-      <c r="V39" s="4"/>
-      <c r="W39" s="4"/>
-      <c r="X39" s="4"/>
-      <c r="Y39" s="4"/>
-      <c r="Z39" s="4"/>
-      <c r="AA39" s="4"/>
-      <c r="AB39" s="4"/>
-      <c r="AC39" s="4"/>
-      <c r="AD39" s="4"/>
-      <c r="AE39" s="4"/>
-      <c r="AF39" s="4"/>
-      <c r="AG39" s="4"/>
-      <c r="AH39" s="4"/>
-      <c r="AI39" s="4"/>
-      <c r="AJ39" s="4"/>
-      <c r="AK39" s="4"/>
-      <c r="AL39" s="4"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2"/>
+      <c r="T39" s="2"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="2"/>
+      <c r="W39" s="2"/>
+      <c r="X39" s="2"/>
+      <c r="Y39" s="2"/>
+      <c r="Z39" s="2"/>
+      <c r="AA39" s="2"/>
+      <c r="AB39" s="2"/>
+      <c r="AC39" s="2"/>
+      <c r="AD39" s="2"/>
+      <c r="AE39" s="2"/>
+      <c r="AF39" s="2"/>
+      <c r="AG39" s="2"/>
+      <c r="AH39" s="2"/>
+      <c r="AI39" s="2"/>
+      <c r="AJ39" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK39" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL39" s="2"/>
     </row>
     <row r="40" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A40" s="4">
+      <c r="A40" s="2">
         <v>37</v>
       </c>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
-      <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
-      <c r="R40" s="4"/>
-      <c r="S40" s="4"/>
-      <c r="T40" s="4"/>
-      <c r="U40" s="4"/>
-      <c r="V40" s="4"/>
-      <c r="W40" s="4"/>
-      <c r="X40" s="4"/>
-      <c r="Y40" s="4"/>
-      <c r="Z40" s="4"/>
-      <c r="AA40" s="4"/>
-      <c r="AB40" s="4"/>
-      <c r="AC40" s="4"/>
-      <c r="AD40" s="4"/>
-      <c r="AE40" s="4"/>
-      <c r="AF40" s="4"/>
-      <c r="AG40" s="4"/>
-      <c r="AH40" s="4"/>
-      <c r="AI40" s="4"/>
-      <c r="AJ40" s="4"/>
-      <c r="AK40" s="4"/>
-      <c r="AL40" s="4"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
+      <c r="T40" s="2"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="2"/>
+      <c r="W40" s="2"/>
+      <c r="X40" s="2"/>
+      <c r="Y40" s="2"/>
+      <c r="Z40" s="2"/>
+      <c r="AA40" s="2"/>
+      <c r="AB40" s="2"/>
+      <c r="AC40" s="2"/>
+      <c r="AD40" s="2"/>
+      <c r="AE40" s="2"/>
+      <c r="AF40" s="2"/>
+      <c r="AG40" s="2"/>
+      <c r="AH40" s="2"/>
+      <c r="AI40" s="2"/>
+      <c r="AJ40" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK40" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL40" s="2"/>
     </row>
     <row r="41" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A41" s="4">
+      <c r="A41" s="2">
         <v>38</v>
       </c>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="4"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
-      <c r="R41" s="4"/>
-      <c r="S41" s="4"/>
-      <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
-      <c r="V41" s="4"/>
-      <c r="W41" s="4"/>
-      <c r="X41" s="4"/>
-      <c r="Y41" s="4"/>
-      <c r="Z41" s="4"/>
-      <c r="AA41" s="4"/>
-      <c r="AB41" s="4"/>
-      <c r="AC41" s="4"/>
-      <c r="AD41" s="4"/>
-      <c r="AE41" s="4"/>
-      <c r="AF41" s="4"/>
-      <c r="AG41" s="4"/>
-      <c r="AH41" s="4"/>
-      <c r="AI41" s="4"/>
-      <c r="AJ41" s="4"/>
-      <c r="AK41" s="4"/>
-      <c r="AL41" s="4"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="2"/>
+      <c r="T41" s="2"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="2"/>
+      <c r="W41" s="2"/>
+      <c r="X41" s="2"/>
+      <c r="Y41" s="2"/>
+      <c r="Z41" s="2"/>
+      <c r="AA41" s="2"/>
+      <c r="AB41" s="2"/>
+      <c r="AC41" s="2"/>
+      <c r="AD41" s="2"/>
+      <c r="AE41" s="2"/>
+      <c r="AF41" s="2"/>
+      <c r="AG41" s="2"/>
+      <c r="AH41" s="2"/>
+      <c r="AI41" s="2"/>
+      <c r="AJ41" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK41" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL41" s="2"/>
     </row>
     <row r="42" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A42" s="4">
+      <c r="A42" s="2">
         <v>39</v>
       </c>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="4"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
-      <c r="Q42" s="4"/>
-      <c r="R42" s="4"/>
-      <c r="S42" s="4"/>
-      <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
-      <c r="V42" s="4"/>
-      <c r="W42" s="4"/>
-      <c r="X42" s="4"/>
-      <c r="Y42" s="4"/>
-      <c r="Z42" s="4"/>
-      <c r="AA42" s="4"/>
-      <c r="AB42" s="4"/>
-      <c r="AC42" s="4"/>
-      <c r="AD42" s="4"/>
-      <c r="AE42" s="4"/>
-      <c r="AF42" s="4"/>
-      <c r="AG42" s="4"/>
-      <c r="AH42" s="4"/>
-      <c r="AI42" s="4"/>
-      <c r="AJ42" s="4"/>
-      <c r="AK42" s="4"/>
-      <c r="AL42" s="4"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="2"/>
+      <c r="T42" s="2"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="2"/>
+      <c r="W42" s="2"/>
+      <c r="X42" s="2"/>
+      <c r="Y42" s="2"/>
+      <c r="Z42" s="2"/>
+      <c r="AA42" s="2"/>
+      <c r="AB42" s="2"/>
+      <c r="AC42" s="2"/>
+      <c r="AD42" s="2"/>
+      <c r="AE42" s="2"/>
+      <c r="AF42" s="2"/>
+      <c r="AG42" s="2"/>
+      <c r="AH42" s="2"/>
+      <c r="AI42" s="2"/>
+      <c r="AJ42" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK42" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL42" s="2"/>
     </row>
     <row r="43" spans="1:38" x14ac:dyDescent="0.3">
-      <c r="A43" s="4">
+      <c r="A43" s="2">
         <v>40</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
-      <c r="Q43" s="4"/>
-      <c r="R43" s="4"/>
-      <c r="S43" s="4"/>
-      <c r="T43" s="4"/>
-      <c r="U43" s="4"/>
-      <c r="V43" s="4"/>
-      <c r="W43" s="4"/>
-      <c r="X43" s="4"/>
-      <c r="Y43" s="4"/>
-      <c r="Z43" s="4"/>
-      <c r="AA43" s="4"/>
-      <c r="AB43" s="4"/>
-      <c r="AC43" s="4"/>
-      <c r="AD43" s="4"/>
-      <c r="AE43" s="4"/>
-      <c r="AF43" s="4"/>
-      <c r="AG43" s="4"/>
-      <c r="AH43" s="4"/>
-      <c r="AI43" s="4"/>
-      <c r="AJ43" s="4"/>
-      <c r="AK43" s="4"/>
-      <c r="AL43" s="4"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="2"/>
+      <c r="T43" s="2"/>
+      <c r="U43" s="2"/>
+      <c r="V43" s="2"/>
+      <c r="W43" s="2"/>
+      <c r="X43" s="2"/>
+      <c r="Y43" s="2"/>
+      <c r="Z43" s="2"/>
+      <c r="AA43" s="2"/>
+      <c r="AB43" s="2"/>
+      <c r="AC43" s="2"/>
+      <c r="AD43" s="2"/>
+      <c r="AE43" s="2"/>
+      <c r="AF43" s="2"/>
+      <c r="AG43" s="2"/>
+      <c r="AH43" s="2"/>
+      <c r="AI43" s="2"/>
+      <c r="AJ43" s="2">
+        <v>927774967</v>
+      </c>
+      <c r="AK43" s="2">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AL43" s="2">
+        <f>SUM(AK4:AK43)</f>
+        <v>11516</v>
+      </c>
     </row>
     <row r="44" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A44" s="4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="49">
   <si>
     <t xml:space="preserve">ном ва насаб </t>
   </si>
@@ -145,6 +145,27 @@
   </si>
   <si>
     <t>Гулов Қурбон</t>
+  </si>
+  <si>
+    <t>Муҳиддинов Шамсиддин</t>
+  </si>
+  <si>
+    <t>бо %</t>
+  </si>
+  <si>
+    <t>м/ҷ</t>
+  </si>
+  <si>
+    <t>м/б/ҷ</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>о/с</t>
+  </si>
+  <si>
+    <t>о/н</t>
   </si>
 </sst>
 </file>
@@ -215,7 +236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -226,6 +247,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -506,7 +529,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AL53"/>
+  <dimension ref="A1:AP53"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -520,12 +543,17 @@
     <col min="13" max="13" width="4.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="4.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="34" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="5.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="34" width="3.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="17.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="39" max="39" width="6.85546875" style="1" customWidth="1"/>
+    <col min="40" max="40" width="6.28515625" style="1" customWidth="1"/>
+    <col min="41" max="41" width="5.42578125" style="1" customWidth="1"/>
+    <col min="42" max="42" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" x14ac:dyDescent="0.3">
@@ -2253,7 +2281,7 @@
       </c>
       <c r="AL32" s="2"/>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>30</v>
       </c>
@@ -2304,7 +2332,7 @@
       </c>
       <c r="AL33" s="2"/>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>31</v>
       </c>
@@ -2355,7 +2383,7 @@
       </c>
       <c r="AL34" s="2"/>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>32</v>
       </c>
@@ -2406,7 +2434,7 @@
       </c>
       <c r="AL35" s="2"/>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>33</v>
       </c>
@@ -2457,11 +2485,13 @@
       </c>
       <c r="AL36" s="2"/>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>34</v>
       </c>
-      <c r="B37" s="2"/>
+      <c r="B37" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
@@ -2477,7 +2507,9 @@
       <c r="O37" s="2"/>
       <c r="P37" s="2"/>
       <c r="Q37" s="2"/>
-      <c r="R37" s="2"/>
+      <c r="R37" s="2">
+        <v>1000</v>
+      </c>
       <c r="S37" s="2"/>
       <c r="T37" s="2"/>
       <c r="U37" s="2"/>
@@ -2500,11 +2532,11 @@
       </c>
       <c r="AK37" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL37" s="2"/>
     </row>
-    <row r="38" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>35</v>
       </c>
@@ -2551,7 +2583,7 @@
       </c>
       <c r="AL38" s="2"/>
     </row>
-    <row r="39" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>36</v>
       </c>
@@ -2598,7 +2630,7 @@
       </c>
       <c r="AL39" s="2"/>
     </row>
-    <row r="40" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>37</v>
       </c>
@@ -2645,7 +2677,7 @@
       </c>
       <c r="AL40" s="2"/>
     </row>
-    <row r="41" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>38</v>
       </c>
@@ -2691,8 +2723,20 @@
         <v>0</v>
       </c>
       <c r="AL41" s="2"/>
-    </row>
-    <row r="42" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="AM41" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AN41" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AO41" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AP41" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>39</v>
       </c>
@@ -2738,8 +2782,20 @@
         <v>0</v>
       </c>
       <c r="AL42" s="2"/>
-    </row>
-    <row r="43" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="AM42" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AN42" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="AO42" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="AP42" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="43" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>40</v>
       </c>
@@ -2786,10 +2842,26 @@
       </c>
       <c r="AL43" s="2">
         <f>SUM(AK4:AK43)</f>
-        <v>11516</v>
-      </c>
-    </row>
-    <row r="44" spans="1:38" x14ac:dyDescent="0.3">
+        <v>12516</v>
+      </c>
+      <c r="AM43" s="6">
+        <f>AL43/26100%</f>
+        <v>47.954022988505749</v>
+      </c>
+      <c r="AN43" s="6">
+        <f>100-AM43</f>
+        <v>52.045977011494251</v>
+      </c>
+      <c r="AO43" s="6">
+        <f>34/87*100</f>
+        <v>39.080459770114942</v>
+      </c>
+      <c r="AP43" s="7">
+        <f>100-39.08</f>
+        <v>60.92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>41</v>
       </c>
@@ -2831,7 +2903,7 @@
       <c r="AK44" s="4"/>
       <c r="AL44" s="4"/>
     </row>
-    <row r="45" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>42</v>
       </c>
@@ -2873,7 +2945,7 @@
       <c r="AK45" s="4"/>
       <c r="AL45" s="4"/>
     </row>
-    <row r="46" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>43</v>
       </c>
@@ -2915,7 +2987,7 @@
       <c r="AK46" s="4"/>
       <c r="AL46" s="4"/>
     </row>
-    <row r="47" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>44</v>
       </c>
@@ -2957,7 +3029,7 @@
       <c r="AK47" s="4"/>
       <c r="AL47" s="4"/>
     </row>
-    <row r="48" spans="1:38" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>45</v>
       </c>
@@ -3214,7 +3286,50 @@
     <mergeCell ref="A1:AK1"/>
     <mergeCell ref="A2:AK2"/>
   </mergeCells>
+  <conditionalFormatting sqref="AM41:AP41">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{498FE68A-3616-43B3-9AEB-DA37194C479E}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{498FE68A-3616-43B3-9AEB-DA37194C479E}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>AM41:AP41</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>